--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_story_details_info[故事详情信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_story_details_info[故事详情信息].xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -76,13 +76,13 @@
     <t>参数2(镜头=时长秒默认1;特效=目标标记空=核心/魔王位;淡入淡出=时长秒默认0.5)</t>
   </si>
   <si>
-    <t>参数3(镜头=缓动DOTween序号默认0;特效=尺寸倍率默认1)</t>
-  </si>
-  <si>
-    <t>参数4(预留)</t>
-  </si>
-  <si>
-    <t>备注</t>
+    <t>参数2(对话=对话框对齐bottom/bottom_left/bottom_right/middle/middle_left/middle_right/top/top_left/top_right,空=bottom下对齐,可接|高亮目标demon魔王核心/crystal掉落魔晶/ui_fight_card手卡/ui_fight_remove删除按钮/ui_fight_att_progress进攻进度,可再接|形状rect方形默认/circle圆形|尺寸倍率默认1;镜头=时长秒默认1;特效=目标标记空=核心/魔王位;淡入淡出=时长秒默认0.5)</t>
+  </si>
+  <si>
+    <t>参数3(对话=偏移X默认0;镜头=缓动DOTween序号默认0;特效=尺寸倍率默认1)</t>
+  </si>
+  <si>
+    <t>参数4(对话=偏移Y默认0)</t>
   </si>
   <si>
     <t>in</t>
@@ -94,39 +94,39 @@
     <t>淡入</t>
   </si>
   <si>
-    <t>1&amp;2</t>
+    <t>1001&amp;1002</t>
+  </si>
+  <si>
+    <t>旁白开场</t>
+  </si>
+  <si>
+    <t>self</t>
+  </si>
+  <si>
+    <t>镜头移向核心</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>介绍核心</t>
+  </si>
+  <si>
+    <t>portal</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>镜头移向传送门</t>
+  </si>
+  <si>
+    <t>1004</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>旁白开场</t>
-  </si>
-  <si>
-    <t>self</t>
-  </si>
-  <si>
-    <t>镜头移向核心</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>介绍核心</t>
-  </si>
-  <si>
-    <t>portal</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>镜头移向传送门</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>介绍传送门</t>
   </si>
   <si>
@@ -136,25 +136,49 @@
     <t>镜头回位(并发)</t>
   </si>
   <si>
-    <t>战斗说明1</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>战斗说明2</t>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>战斗说明</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>|ui_fight_att_progress</t>
+  </si>
+  <si>
+    <t>3001</t>
+  </si>
+  <si>
+    <t>|crystal|circle</t>
+  </si>
+  <si>
+    <t>拾晶说明</t>
   </si>
   <si>
     <t>core</t>
   </si>
   <si>
-    <t>镜头移向核心(并发)</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>拾晶说明</t>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>|ui_fight_card</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>|demon|circle</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>|ui_fight_remove</t>
   </si>
 </sst>
 </file>
@@ -558,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,17 +726,8 @@
       <c r="F5" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="J5" s="0" t="s">
         <v>27</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="0" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -732,19 +747,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>27</v>
-      </c>
       <c r="J6" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -764,19 +773,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="0" t="s">
         <v>31</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="0" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -796,19 +796,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="J8" s="0" t="s">
         <v>34</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="0" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -828,16 +822,16 @@
         <v>0</v>
       </c>
       <c r="F9" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="0" t="s">
-        <v>27</v>
-      </c>
       <c r="H9" s="0" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>37</v>
@@ -865,12 +859,6 @@
       <c r="G10" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="0" t="s">
-        <v>27</v>
-      </c>
       <c r="J10" s="0" t="s">
         <v>39</v>
       </c>
@@ -892,10 +880,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -915,15 +903,18 @@
         <v>0</v>
       </c>
       <c r="F12" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="0" t="s">
         <v>41</v>
-      </c>
-      <c r="J12" s="0" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="B13" s="0">
         <v>3</v>
@@ -932,100 +923,135 @@
         <v>1</v>
       </c>
       <c r="D13" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>24</v>
+        <v>45</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="0" t="s">
+        <v>36</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>3002</v>
+        <v>1008</v>
       </c>
       <c r="B14" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="0">
         <v>0</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>3003</v>
+        <v>2003</v>
       </c>
       <c r="B15" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" s="0">
         <v>3</v>
       </c>
       <c r="D15" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>24</v>
+        <v>49</v>
+      </c>
+      <c r="I15" s="0" t="s">
+        <v>50</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>1008</v>
+        <v>2004</v>
       </c>
       <c r="B16" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="0">
         <v>4</v>
       </c>
       <c r="D16" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="0">
         <v>0</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>2005</v>
+      </c>
+      <c r="B17" s="0">
+        <v>2</v>
+      </c>
+      <c r="C17" s="0">
+        <v>5</v>
+      </c>
+      <c r="D17" s="0">
+        <v>1</v>
+      </c>
+      <c r="E17" s="0">
+        <v>0</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="J17" s="0" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
